--- a/data/raw/관세청/Import Export Performance by Commodity and Country(GW)/Soybean Oil/1507.10/Food use (.1000)/China.xlsx
+++ b/data/raw/관세청/Import Export Performance by Commodity and Country(GW)/Soybean Oil/1507.10/Food use (.1000)/China.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\데이터플랫폼팀\00 데이터플랫폼팀_공유\데이터플랫폼팀(23.03~)\08 데이터 분석\00 분석과제정의서\☆구매\수입원료\대두유\데이터\외부\경제, 무역\관세청\9개년_품목별 국가별 수출입실적\대두유\1507.10\식품용(.1000)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\데이터플랫폼팀\00 데이터플랫폼팀_공유\데이터플랫폼팀(23.03~)\08 데이터 분석\00 분석과제정의서\☆구매\수입원료\대두유\데이터\외부\경제, 무역\관세청\15개년_품목별 국가별 수출입실적\대두유\1507.10\식품용(.1000)\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -904,18 +904,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C5" s="2">
-        <v>0</v>
-      </c>
-      <c r="D5" s="2">
-        <v>0</v>
-      </c>
-      <c r="E5" s="2">
-        <v>0</v>
-      </c>
-      <c r="F5" s="2">
-        <v>0</v>
-      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
@@ -925,18 +917,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C6" s="2">
-        <v>0</v>
-      </c>
-      <c r="D6" s="2">
-        <v>0</v>
-      </c>
-      <c r="E6" s="2">
-        <v>0</v>
-      </c>
-      <c r="F6" s="2">
-        <v>0</v>
-      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
@@ -946,18 +930,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C7" s="2">
-        <v>0</v>
-      </c>
-      <c r="D7" s="2">
-        <v>0</v>
-      </c>
-      <c r="E7" s="2">
-        <v>0</v>
-      </c>
-      <c r="F7" s="2">
-        <v>0</v>
-      </c>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
@@ -967,18 +943,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C8" s="2">
-        <v>0</v>
-      </c>
-      <c r="D8" s="2">
-        <v>0</v>
-      </c>
-      <c r="E8" s="2">
-        <v>0</v>
-      </c>
-      <c r="F8" s="2">
-        <v>0</v>
-      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
@@ -1009,18 +977,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C10" s="2">
-        <v>0</v>
-      </c>
-      <c r="D10" s="2">
-        <v>0</v>
-      </c>
-      <c r="E10" s="2">
-        <v>0</v>
-      </c>
-      <c r="F10" s="2">
-        <v>0</v>
-      </c>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
@@ -1051,18 +1011,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C12" s="2">
-        <v>0</v>
-      </c>
-      <c r="D12" s="2">
-        <v>0</v>
-      </c>
-      <c r="E12" s="2">
-        <v>0</v>
-      </c>
-      <c r="F12" s="2">
-        <v>0</v>
-      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
@@ -1072,18 +1024,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C13" s="2">
-        <v>0</v>
-      </c>
-      <c r="D13" s="2">
-        <v>0</v>
-      </c>
-      <c r="E13" s="2">
-        <v>0</v>
-      </c>
-      <c r="F13" s="2">
-        <v>0</v>
-      </c>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
@@ -1093,18 +1037,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C14" s="2">
-        <v>0</v>
-      </c>
-      <c r="D14" s="2">
-        <v>0</v>
-      </c>
-      <c r="E14" s="2">
-        <v>0</v>
-      </c>
-      <c r="F14" s="2">
-        <v>0</v>
-      </c>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
     </row>
     <row r="15" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
@@ -1174,18 +1110,10 @@
         <f t="shared" ref="B3:B14" si="0">C3-E3</f>
         <v>0</v>
       </c>
-      <c r="C3" s="2">
-        <v>0</v>
-      </c>
-      <c r="D3" s="2">
-        <v>0</v>
-      </c>
-      <c r="E3" s="2">
-        <v>0</v>
-      </c>
-      <c r="F3" s="2">
-        <v>0</v>
-      </c>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -1195,18 +1123,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C4" s="2">
-        <v>0</v>
-      </c>
-      <c r="D4" s="2">
-        <v>0</v>
-      </c>
-      <c r="E4" s="2">
-        <v>0</v>
-      </c>
-      <c r="F4" s="2">
-        <v>0</v>
-      </c>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
@@ -1237,18 +1157,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C6" s="2">
-        <v>0</v>
-      </c>
-      <c r="D6" s="2">
-        <v>0</v>
-      </c>
-      <c r="E6" s="2">
-        <v>0</v>
-      </c>
-      <c r="F6" s="2">
-        <v>0</v>
-      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
@@ -1258,18 +1170,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C7" s="2">
-        <v>0</v>
-      </c>
-      <c r="D7" s="2">
-        <v>0</v>
-      </c>
-      <c r="E7" s="2">
-        <v>0</v>
-      </c>
-      <c r="F7" s="2">
-        <v>0</v>
-      </c>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
@@ -1342,18 +1246,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C11" s="2">
-        <v>0</v>
-      </c>
-      <c r="D11" s="2">
-        <v>0</v>
-      </c>
-      <c r="E11" s="2">
-        <v>0</v>
-      </c>
-      <c r="F11" s="2">
-        <v>0</v>
-      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
@@ -1363,18 +1259,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C12" s="2">
-        <v>0</v>
-      </c>
-      <c r="D12" s="2">
-        <v>0</v>
-      </c>
-      <c r="E12" s="2">
-        <v>0</v>
-      </c>
-      <c r="F12" s="2">
-        <v>0</v>
-      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
@@ -1405,18 +1293,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C14" s="2">
-        <v>0</v>
-      </c>
-      <c r="D14" s="2">
-        <v>0</v>
-      </c>
-      <c r="E14" s="2">
-        <v>0</v>
-      </c>
-      <c r="F14" s="2">
-        <v>0</v>
-      </c>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
     </row>
     <row r="15" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
@@ -1486,18 +1366,10 @@
         <f t="shared" ref="B3:B14" si="0">C3-E3</f>
         <v>0</v>
       </c>
-      <c r="C3" s="2">
-        <v>0</v>
-      </c>
-      <c r="D3" s="2">
-        <v>0</v>
-      </c>
-      <c r="E3" s="2">
-        <v>0</v>
-      </c>
-      <c r="F3" s="2">
-        <v>0</v>
-      </c>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -1507,18 +1379,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C4" s="2">
-        <v>0</v>
-      </c>
-      <c r="D4" s="2">
-        <v>0</v>
-      </c>
-      <c r="E4" s="2">
-        <v>0</v>
-      </c>
-      <c r="F4" s="2">
-        <v>0</v>
-      </c>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
@@ -1528,18 +1392,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C5" s="2">
-        <v>0</v>
-      </c>
-      <c r="D5" s="2">
-        <v>0</v>
-      </c>
-      <c r="E5" s="2">
-        <v>0</v>
-      </c>
-      <c r="F5" s="2">
-        <v>0</v>
-      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
@@ -1591,18 +1447,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C8" s="2">
-        <v>0</v>
-      </c>
-      <c r="D8" s="2">
-        <v>0</v>
-      </c>
-      <c r="E8" s="2">
-        <v>0</v>
-      </c>
-      <c r="F8" s="2">
-        <v>0</v>
-      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
@@ -1696,18 +1544,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C13" s="2">
-        <v>0</v>
-      </c>
-      <c r="D13" s="2">
-        <v>0</v>
-      </c>
-      <c r="E13" s="2">
-        <v>0</v>
-      </c>
-      <c r="F13" s="2">
-        <v>0</v>
-      </c>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
@@ -2527,18 +2367,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C8" s="2">
-        <v>0</v>
-      </c>
-      <c r="D8" s="2">
-        <v>0</v>
-      </c>
-      <c r="E8" s="2">
-        <v>0</v>
-      </c>
-      <c r="F8" s="2">
-        <v>0</v>
-      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
@@ -2611,18 +2443,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C12" s="2">
-        <v>0</v>
-      </c>
-      <c r="D12" s="2">
-        <v>0</v>
-      </c>
-      <c r="E12" s="2">
-        <v>0</v>
-      </c>
-      <c r="F12" s="2">
-        <v>0</v>
-      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
@@ -2734,20 +2558,10 @@
         <f t="shared" ref="B3:F14" si="0">C3-E3</f>
         <v>0</v>
       </c>
-      <c r="C3" s="2">
-        <v>0</v>
-      </c>
-      <c r="D3" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E3" s="2">
-        <v>0</v>
-      </c>
-      <c r="F3" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -2757,20 +2571,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C4" s="2">
-        <v>0</v>
-      </c>
-      <c r="D4" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E4" s="2">
-        <v>0</v>
-      </c>
-      <c r="F4" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
@@ -2843,18 +2647,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C8" s="2">
-        <v>0</v>
-      </c>
-      <c r="D8" s="2">
-        <v>0</v>
-      </c>
-      <c r="E8" s="2">
-        <v>0</v>
-      </c>
-      <c r="F8" s="2">
-        <v>0</v>
-      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
@@ -3047,7 +2843,7 @@
         <v>0</v>
       </c>
       <c r="B3" s="2">
-        <f t="shared" ref="B3:F14" si="0">C3-E3</f>
+        <f t="shared" ref="B3:B14" si="0">C3-E3</f>
         <v>-3</v>
       </c>
       <c r="C3" s="2">
@@ -3166,12 +2962,20 @@
       </c>
       <c r="B9" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
+        <v>4124</v>
+      </c>
+      <c r="C9" s="2">
+        <v>4131</v>
+      </c>
+      <c r="D9" s="2">
+        <v>1800</v>
+      </c>
+      <c r="E9" s="2">
+        <v>7</v>
+      </c>
+      <c r="F9" s="2">
+        <v>3</v>
+      </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
@@ -3244,23 +3048,23 @@
       </c>
       <c r="B15" s="5">
         <f>SUM(B3:B14)</f>
-        <v>-12368711</v>
+        <v>-12364587</v>
       </c>
       <c r="C15" s="5">
         <f t="shared" ref="C15:F15" si="1">SUM(C3:C14)</f>
-        <v>2335</v>
+        <v>6466</v>
       </c>
       <c r="D15" s="5">
         <f t="shared" si="1"/>
-        <v>1080</v>
+        <v>2880</v>
       </c>
       <c r="E15" s="5">
         <f t="shared" si="1"/>
-        <v>12371046</v>
+        <v>12371053</v>
       </c>
       <c r="F15" s="5">
         <f t="shared" si="1"/>
-        <v>10031413</v>
+        <v>10031416</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="17.25" thickTop="1" x14ac:dyDescent="0.3"/>
@@ -4914,29 +4718,21 @@
         <v>0</v>
       </c>
       <c r="B3" s="2">
-        <f>E3-C3</f>
-        <v>0</v>
-      </c>
-      <c r="C3" s="2">
-        <v>0</v>
-      </c>
-      <c r="D3" s="2">
-        <v>0</v>
-      </c>
-      <c r="E3" s="2">
-        <v>0</v>
-      </c>
-      <c r="F3" s="2">
-        <v>0</v>
-      </c>
+        <f t="shared" ref="B3:B14" si="0">C3-E3</f>
+        <v>0</v>
+      </c>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B4" s="2">
-        <f t="shared" ref="B4:B15" si="0">E4-C4</f>
-        <v>-2150</v>
+        <f t="shared" si="0"/>
+        <v>2150</v>
       </c>
       <c r="C4" s="2">
         <v>2150</v>
@@ -4959,18 +4755,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C5" s="2">
-        <v>0</v>
-      </c>
-      <c r="D5" s="2">
-        <v>0</v>
-      </c>
-      <c r="E5" s="2">
-        <v>0</v>
-      </c>
-      <c r="F5" s="2">
-        <v>0</v>
-      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
@@ -4980,18 +4768,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C6" s="2">
-        <v>0</v>
-      </c>
-      <c r="D6" s="2">
-        <v>0</v>
-      </c>
-      <c r="E6" s="2">
-        <v>0</v>
-      </c>
-      <c r="F6" s="2">
-        <v>0</v>
-      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
@@ -5001,18 +4781,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C7" s="2">
-        <v>0</v>
-      </c>
-      <c r="D7" s="2">
-        <v>0</v>
-      </c>
-      <c r="E7" s="2">
-        <v>0</v>
-      </c>
-      <c r="F7" s="2">
-        <v>0</v>
-      </c>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
@@ -5022,18 +4794,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C8" s="2">
-        <v>0</v>
-      </c>
-      <c r="D8" s="2">
-        <v>0</v>
-      </c>
-      <c r="E8" s="2">
-        <v>0</v>
-      </c>
-      <c r="F8" s="2">
-        <v>0</v>
-      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
@@ -5043,18 +4807,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C9" s="2">
-        <v>0</v>
-      </c>
-      <c r="D9" s="2">
-        <v>0</v>
-      </c>
-      <c r="E9" s="2">
-        <v>0</v>
-      </c>
-      <c r="F9" s="2">
-        <v>0</v>
-      </c>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
@@ -5064,18 +4820,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C10" s="2">
-        <v>0</v>
-      </c>
-      <c r="D10" s="2">
-        <v>0</v>
-      </c>
-      <c r="E10" s="2">
-        <v>0</v>
-      </c>
-      <c r="F10" s="2">
-        <v>0</v>
-      </c>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
@@ -5085,18 +4833,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C11" s="2">
-        <v>0</v>
-      </c>
-      <c r="D11" s="2">
-        <v>0</v>
-      </c>
-      <c r="E11" s="2">
-        <v>0</v>
-      </c>
-      <c r="F11" s="2">
-        <v>0</v>
-      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
@@ -5106,18 +4846,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C12" s="2">
-        <v>0</v>
-      </c>
-      <c r="D12" s="2">
-        <v>0</v>
-      </c>
-      <c r="E12" s="2">
-        <v>0</v>
-      </c>
-      <c r="F12" s="2">
-        <v>0</v>
-      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
@@ -5127,18 +4859,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C13" s="2">
-        <v>0</v>
-      </c>
-      <c r="D13" s="2">
-        <v>0</v>
-      </c>
-      <c r="E13" s="2">
-        <v>0</v>
-      </c>
-      <c r="F13" s="2">
-        <v>0</v>
-      </c>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
@@ -5146,7 +4870,7 @@
       </c>
       <c r="B14" s="2">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>-20</v>
       </c>
       <c r="C14" s="2">
         <v>8</v>
@@ -5166,23 +4890,23 @@
         <v>13</v>
       </c>
       <c r="B15" s="5">
-        <f t="shared" si="0"/>
-        <v>-2130</v>
+        <f>SUM(B3:B14)</f>
+        <v>2130</v>
       </c>
       <c r="C15" s="5">
-        <f t="shared" ref="C15" si="1">SUM(C3:C14)</f>
+        <f t="shared" ref="C15:F15" si="1">SUM(C3:C14)</f>
         <v>2158</v>
       </c>
       <c r="D15" s="5">
-        <f t="shared" ref="D15" si="2">SUM(D3:D14)</f>
+        <f t="shared" si="1"/>
         <v>43</v>
       </c>
       <c r="E15" s="5">
-        <f t="shared" ref="E15:F15" si="3">SUM(E3:E14)</f>
+        <f t="shared" si="1"/>
         <v>28</v>
       </c>
       <c r="F15" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
     </row>
@@ -5190,6 +4914,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -5271,18 +4996,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C5" s="2">
-        <v>0</v>
-      </c>
-      <c r="D5" s="2">
-        <v>0</v>
-      </c>
-      <c r="E5" s="2">
-        <v>0</v>
-      </c>
-      <c r="F5" s="2">
-        <v>0</v>
-      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
@@ -5292,18 +5009,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C6" s="2">
-        <v>0</v>
-      </c>
-      <c r="D6" s="2">
-        <v>0</v>
-      </c>
-      <c r="E6" s="2">
-        <v>0</v>
-      </c>
-      <c r="F6" s="2">
-        <v>0</v>
-      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
@@ -5313,18 +5022,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C7" s="2">
-        <v>0</v>
-      </c>
-      <c r="D7" s="2">
-        <v>0</v>
-      </c>
-      <c r="E7" s="2">
-        <v>0</v>
-      </c>
-      <c r="F7" s="2">
-        <v>0</v>
-      </c>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
@@ -5334,18 +5035,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C8" s="2">
-        <v>0</v>
-      </c>
-      <c r="D8" s="2">
-        <v>0</v>
-      </c>
-      <c r="E8" s="2">
-        <v>0</v>
-      </c>
-      <c r="F8" s="2">
-        <v>0</v>
-      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
@@ -5355,18 +5048,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C9" s="2">
-        <v>0</v>
-      </c>
-      <c r="D9" s="2">
-        <v>0</v>
-      </c>
-      <c r="E9" s="2">
-        <v>0</v>
-      </c>
-      <c r="F9" s="2">
-        <v>0</v>
-      </c>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
@@ -5376,18 +5061,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C10" s="2">
-        <v>0</v>
-      </c>
-      <c r="D10" s="2">
-        <v>0</v>
-      </c>
-      <c r="E10" s="2">
-        <v>0</v>
-      </c>
-      <c r="F10" s="2">
-        <v>0</v>
-      </c>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
@@ -5418,18 +5095,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C12" s="2">
-        <v>0</v>
-      </c>
-      <c r="D12" s="2">
-        <v>0</v>
-      </c>
-      <c r="E12" s="2">
-        <v>0</v>
-      </c>
-      <c r="F12" s="2">
-        <v>0</v>
-      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
@@ -5439,18 +5108,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C13" s="2">
-        <v>0</v>
-      </c>
-      <c r="D13" s="2">
-        <v>0</v>
-      </c>
-      <c r="E13" s="2">
-        <v>0</v>
-      </c>
-      <c r="F13" s="2">
-        <v>0</v>
-      </c>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
